--- a/src-tauri/tests/fixtures/2026年4月分析/活动量/北京中言.xlsx
+++ b/src-tauri/tests/fixtures/2026年4月分析/活动量/北京中言.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="填写说明" sheetId="4" r:id="rId1"/>
-    <sheet name="写字楼和商业综合体类" sheetId="2" r:id="rId2"/>
+    <sheet name="商写类" sheetId="2" r:id="rId2"/>
     <sheet name="酒店类" sheetId="1" r:id="rId3"/>
     <sheet name="保险类" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">写字楼和商业综合体类!$A$3:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">商写类!$A$3:$Q$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
